--- a/output/pdf_financials_xlsx/STKT.xlsx
+++ b/output/pdf_financials_xlsx/STKT.xlsx
@@ -57,10 +57,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -490,15 +491,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="6">
@@ -524,15 +521,11 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -541,15 +534,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="9">
@@ -558,15 +547,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -575,15 +560,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="11">
@@ -609,15 +590,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -626,15 +603,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -643,15 +616,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -660,15 +629,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.016</v>
       </c>
     </row>
     <row r="16">
@@ -694,15 +659,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -762,15 +723,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -779,15 +736,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -881,15 +834,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0.016</v>
       </c>
     </row>
     <row r="29">
@@ -2085,15 +2034,11 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2102,15 +2047,11 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2119,15 +2060,11 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="103">
@@ -2136,15 +2073,11 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -2153,15 +2086,11 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0.155</v>
       </c>
     </row>
     <row r="105">
@@ -2170,15 +2099,11 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2187,15 +2112,11 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.195</v>
       </c>
     </row>
     <row r="107">
@@ -2204,15 +2125,11 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2221,15 +2138,11 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2238,15 +2151,11 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2255,15 +2164,11 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2272,15 +2177,11 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2289,15 +2190,11 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2306,15 +2203,11 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2323,15 +2216,11 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2340,15 +2229,11 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2357,15 +2242,11 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2374,15 +2255,11 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2391,15 +2268,11 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2408,10 +2281,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>-0.594</v>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
@@ -2425,15 +2296,11 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2442,15 +2309,11 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2459,15 +2322,11 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2476,15 +2335,11 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2493,15 +2348,11 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2510,15 +2361,11 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2527,15 +2374,11 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2561,15 +2404,11 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2578,10 +2417,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.423</v>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
@@ -2595,15 +2432,11 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0.827</v>
       </c>
     </row>
     <row r="131">
@@ -2612,15 +2445,11 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2629,15 +2458,11 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.168</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>-0.388</v>
       </c>
     </row>
     <row r="133">
@@ -2646,15 +2471,11 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>0.439</v>
       </c>
     </row>
     <row r="134">
@@ -2663,15 +2484,11 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2680,15 +2497,11 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>0.002</v>
       </c>
     </row>
   </sheetData>
@@ -2702,7 +2515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2712,32 +2525,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Statement</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Line item (as printed)</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Canonical key</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -2760,10 +2573,10 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="5" t="n">
         <v>2.025</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="5" t="n">
         <v>0.031</v>
       </c>
     </row>
@@ -2784,7 +2597,7 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>7538.3</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -2810,11 +2623,813 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>2.025</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>0.031</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Adjustments required for presenting Cash flows and cash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Adjustments required for presenting Cash flows and cash equivalents from operating activities (Appendix A): 180</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" s="5" t="n">
+        <v>48.076</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Shares issuance and premium on shares -</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" s="5" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Repayment of loans -</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Cash from a reverse acquisition -</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" s="5" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Net cash provided by financing activities -</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Exchange rate differences on balances of cash and cash equivalents 52</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" s="5" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at the beginning of year 439</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0.827</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at the end of year 319</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.439</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>*See Note 1 A for reverse acquisition</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Appendix A - Adjustments required for presenting cash flows from operating activities:</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Significant non-cash transactions</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Depreciation 3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Significant non-cash transactions</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Share-based payments -</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Significant non-cash transactions</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Issuance costs in a reverse acquisition -</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" s="5" t="n">
+        <v>47.695</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Changes in operating assets and liabilities</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Increase in accounts payable 180</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.155</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Changes in operating assets and liabilities</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Decrease (Increase) in inventories -</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ChangeInInventory</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Changes in operating assets and liabilities</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Increase in trade accounts payable                                      (45)                  ) 18(          (119)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" s="5" t="n">
+        <v>48.076</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>INVESTING AND FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Board of Directors and a director. Note 1 61</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Note 1 - General</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Stickit LTD develop, market and sell high-quality "Cannabis Sticks" based on a registered PCT patent no. 11582996 B2, for which the patent application was assigned to the Company for $ 0.001 on</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" s="5" t="n">
+        <v>2.021</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>STICKIT TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Note 2 0 2 5 2 0 2 4 * 2 0</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" s="5" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>STICKIT TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Revenues 8 -</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" s="5" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>STICKIT TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Cost of revenue 9 3</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>STICKIT TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Gross (loss) profit (3)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" s="5" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>-0.014</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>STICKIT TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Research and development expenses 10 135</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ResearchAndDevelopment</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>STICKIT TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>General and administrative expenses 11 355</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0.307</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>STICKIT TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Issuance costs in a reverse acquisition 1A -</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" s="5" t="n">
+        <v>47.695</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>STICKIT TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>STICKIT TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Equity in net loss of investees 5 -</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" s="5" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>STICKIT TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Finance expense -</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" s="5" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>STICKIT TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Finance income 6</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>or loss</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Foreign currencies translation adjustments 52</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" s="5" t="n">
+        <v>-0.165</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>or loss</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Equity reserve – related party transaction 13</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>
